--- a/banco_de_senhas_automatizado.xlsx
+++ b/banco_de_senhas_automatizado.xlsx
@@ -473,11 +473,11 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-30 15:24:35</t>
+          <t>2026-08-29 15:24:35</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
